--- a/docs/таблица Ганнт.xlsx
+++ b/docs/таблица Ганнт.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A8A3BF-2A23-49C0-8750-E37F84566150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>План проекта (Гантт) · пары 5–30 · магазин обуви</t>
   </si>
@@ -166,19 +165,16 @@
     <t>Команда (ФИО):</t>
   </si>
   <si>
-    <t>в работе</t>
-  </si>
-  <si>
-    <t>Зоидова, Подгорнова</t>
-  </si>
-  <si>
     <t>сделано</t>
+  </si>
+  <si>
+    <t>Зоидова, Подгорнова, Мингазова</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -577,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -636,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -670,7 +666,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -687,7 +683,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -857,7 +853,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E5:E17" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E5:E17">
       <formula1>"не начато,в работе,сделано"</formula1>
     </dataValidation>
   </dataValidations>
